--- a/nursing/フォーマット/03_就労支援記録様式/03_モニタリング記録（就労）.xlsx
+++ b/nursing/フォーマット/03_就労支援記録様式/03_モニタリング記録（就労）.xlsx
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="7">
+  <fonts count="8">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -34,8 +34,14 @@
     <font>
       <name val="Meiryo UI"/>
       <b val="1"/>
-      <color rgb="FF0E7490"/>
+      <color rgb="FFDC2626"/>
       <sz val="8"/>
+    </font>
+    <font>
+      <name val="Meiryo UI"/>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <sz val="9"/>
     </font>
     <font>
       <name val="Meiryo UI"/>
@@ -50,7 +56,7 @@
       <name val="Meiryo UI"/>
       <b val="1"/>
       <color rgb="FFFFFFFF"/>
-      <sz val="9"/>
+      <sz val="10"/>
     </font>
     <font>
       <name val="Meiryo UI"/>
@@ -68,12 +74,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFCFFAFE"/>
+        <fgColor rgb="FF0E7490"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF0E7490"/>
+        <fgColor rgb="FFCFFAFE"/>
       </patternFill>
     </fill>
     <fill>
@@ -100,7 +106,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -109,15 +115,24 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -485,251 +500,304 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H20"/>
+  <dimension ref="A1:H26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="26" customWidth="1" min="1" max="1"/>
+    <col width="7" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="24" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
     <col width="14" customWidth="1" min="6" max="6"/>
-    <col width="14" customWidth="1" min="7" max="7"/>
-    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="8" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>モニタリング記録（就労継続支援A型・B型用）</t>
+          <t>モニタリング記録（就労継続支援A型・B型）</t>
         </is>
       </c>
     </row>
     <row r="2" ht="20" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>【モニタリング頻度】就労継続支援は原則6ヶ月毎（状況変化時は随時）。記録を保管し、個別支援計画の見直しに活用すること。</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="22" customHeight="1">
+          <t>【実施頻度】原則6ヶ月ごと。状態変化時・サービス内容変更時は随時実施。利用者宅または事業所での面談が望ましい。</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="20" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
+          <t>【基本情報】</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="22" customHeight="1">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
           <t>利用者氏名</t>
         </is>
       </c>
-      <c r="C3" s="4" t="inlineStr">
+      <c r="C4" s="5" t="inlineStr">
         <is>
           <t>（様）</t>
         </is>
       </c>
-      <c r="E3" s="3" t="inlineStr">
-        <is>
-          <t>障害種別</t>
-        </is>
-      </c>
-      <c r="G3" s="4" t="inlineStr">
-        <is>
-          <t>身体 / 精神 / 知的 / 難病</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="22" customHeight="1">
-      <c r="A4" s="3" t="inlineStr">
-        <is>
-          <t>事業所名</t>
-        </is>
-      </c>
-      <c r="C4" s="4" t="inlineStr"/>
-      <c r="E4" s="3" t="inlineStr">
+      <c r="F4" s="4" t="inlineStr">
+        <is>
+          <t>実施日</t>
+        </is>
+      </c>
+      <c r="H4" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　　年　月　日</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="22" customHeight="1">
+      <c r="A5" s="4" t="inlineStr">
         <is>
           <t>サービス種別</t>
         </is>
       </c>
-      <c r="G4" s="4" t="inlineStr">
-        <is>
-          <t>就労継続支援A型 / B型</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="22" customHeight="1">
-      <c r="A5" s="3" t="inlineStr">
-        <is>
-          <t>モニタリング実施日</t>
-        </is>
-      </c>
-      <c r="C5" s="4" t="inlineStr">
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>就労継続支援　A型 / B型</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>実施者（サービス管理責任者）</t>
+        </is>
+      </c>
+      <c r="H5" s="5" t="inlineStr"/>
+    </row>
+    <row r="6" ht="22" customHeight="1">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>個別支援計画の期間</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　年　月〜　年　月</t>
+        </is>
+      </c>
+      <c r="F6" s="4" t="inlineStr">
+        <is>
+          <t>前回モニタリング日</t>
+        </is>
+      </c>
+      <c r="H6" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">　　年　月　日</t>
         </is>
       </c>
-      <c r="E5" s="3" t="inlineStr">
-        <is>
-          <t>実施者（サビ管）</t>
-        </is>
-      </c>
-      <c r="G5" s="4" t="inlineStr"/>
-    </row>
-    <row r="6" ht="22" customHeight="1">
-      <c r="A6" s="3" t="inlineStr">
-        <is>
-          <t>前回モニタリング日</t>
-        </is>
-      </c>
-      <c r="C6" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">　　年　月　日</t>
-        </is>
-      </c>
-      <c r="E6" s="3" t="inlineStr">
-        <is>
-          <t>個別支援計画の期間</t>
-        </is>
-      </c>
-      <c r="G6" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">　　年　月〜　　年　月</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="20" customHeight="1">
-      <c r="A7" s="5" t="inlineStr">
-        <is>
-          <t>【目標の達成状況】（個別支援計画の目標ごとに確認）</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="90" customHeight="1">
-      <c r="A8" s="6" t="inlineStr">
-        <is>
-          <t>目標①「　　　　　　　」
-→達成度：達成 / ほぼ達成 / 未達成　　状況：
-目標②「　　　　　　　」
-→達成度：達成 / ほぼ達成 / 未達成　　状況：</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="20" customHeight="1">
-      <c r="A9" s="5" t="inlineStr">
-        <is>
-          <t>【本人の意向・満足度】（本人から聴取した内容）</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="60" customHeight="1">
-      <c r="A10" s="6" t="inlineStr">
-        <is>
-          <t>サービスへの満足度：満足 / ほぼ満足 / 不満　　　理由：
-本人の希望・要望：</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="20" customHeight="1">
-      <c r="A11" s="5" t="inlineStr">
-        <is>
-          <t>【就労・作業状況】</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="60" customHeight="1">
-      <c r="A12" s="6" t="inlineStr">
-        <is>
-          <t>出席日数（当月）：　日/　日（出席率：　　%）
-主な作業内容：
-体調・コンディション：</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="20" customHeight="1">
-      <c r="A13" s="5" t="inlineStr">
+    </row>
+    <row r="7" ht="22" customHeight="1">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>参加者</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>本人 ・ 家族（　　）・ 担当職員 ・ 相談支援専門員 ・ その他（　　）</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>次回モニタリング予定</t>
+        </is>
+      </c>
+      <c r="H7" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　　年　月　日頃</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="20" customHeight="1">
+      <c r="A8" s="3" t="inlineStr">
+        <is>
+          <t>【個別支援計画 目標の達成状況】</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="40" customHeight="1">
+      <c r="A9" s="6" t="inlineStr"/>
+      <c r="B9" s="6" t="inlineStr"/>
+      <c r="C9" s="6" t="inlineStr"/>
+      <c r="D9" s="6" t="inlineStr"/>
+      <c r="E9" s="6" t="inlineStr"/>
+      <c r="F9" s="6" t="inlineStr"/>
+      <c r="G9" s="6" t="inlineStr"/>
+      <c r="H9" s="6" t="inlineStr"/>
+    </row>
+    <row r="10" ht="40" customHeight="1">
+      <c r="A10" s="5" t="inlineStr"/>
+      <c r="B10" s="5" t="inlineStr"/>
+      <c r="C10" s="7" t="inlineStr"/>
+      <c r="D10" s="5" t="inlineStr"/>
+      <c r="E10" s="5" t="inlineStr"/>
+      <c r="F10" s="5" t="inlineStr"/>
+      <c r="G10" s="5" t="inlineStr"/>
+      <c r="H10" s="5" t="inlineStr"/>
+    </row>
+    <row r="11" ht="40" customHeight="1">
+      <c r="A11" s="5" t="inlineStr"/>
+      <c r="B11" s="5" t="inlineStr"/>
+      <c r="C11" s="5" t="inlineStr"/>
+      <c r="D11" s="5" t="inlineStr"/>
+      <c r="E11" s="5" t="inlineStr"/>
+      <c r="F11" s="5" t="inlineStr"/>
+      <c r="G11" s="5" t="inlineStr"/>
+      <c r="H11" s="5" t="inlineStr"/>
+    </row>
+    <row r="12" ht="40" customHeight="1">
+      <c r="A12" s="5" t="inlineStr"/>
+      <c r="B12" s="5" t="inlineStr"/>
+      <c r="C12" s="5" t="inlineStr"/>
+      <c r="D12" s="5" t="inlineStr"/>
+      <c r="E12" s="5" t="inlineStr"/>
+      <c r="F12" s="5" t="inlineStr"/>
+      <c r="G12" s="5" t="inlineStr"/>
+      <c r="H12" s="5" t="inlineStr"/>
+    </row>
+    <row r="13" ht="40" customHeight="1">
+      <c r="A13" s="5" t="inlineStr"/>
+      <c r="B13" s="5" t="inlineStr"/>
+      <c r="C13" s="5" t="inlineStr"/>
+      <c r="D13" s="5" t="inlineStr"/>
+      <c r="E13" s="5" t="inlineStr"/>
+      <c r="F13" s="5" t="inlineStr"/>
+      <c r="G13" s="5" t="inlineStr"/>
+      <c r="H13" s="5" t="inlineStr"/>
+    </row>
+    <row r="14" ht="20" customHeight="1">
+      <c r="A14" s="3" t="inlineStr">
+        <is>
+          <t>【出席・就労状況（モニタリング期間中）】</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="60" customHeight="1">
+      <c r="A15" s="8" t="inlineStr">
+        <is>
+          <t>出席日数：　日/　日（出席率：　　%）　欠席日数：　日　早退：　回　遅刻：　回
+主な作業内容：　　　　　　　作業能力の変化：向上 / 不変 / 低下（理由：　　　）
+工賃実績（B型）：当月　　　　円　年度累計平均　　　　円</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="20" customHeight="1">
+      <c r="A16" s="3" t="inlineStr">
         <is>
           <t>【健康・生活状況の変化】</t>
         </is>
       </c>
     </row>
-    <row r="14" ht="50" customHeight="1">
-      <c r="A14" s="6" t="inlineStr">
-        <is>
-          <t>医療機関受診状況：
-生活環境の変化：
-服薬状況：</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="20" customHeight="1">
-      <c r="A15" s="5" t="inlineStr">
-        <is>
-          <t>【支援内容の評価・課題】</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="60" customHeight="1">
-      <c r="A16" s="6" t="inlineStr"/>
-    </row>
-    <row r="17" ht="20" customHeight="1">
-      <c r="A17" s="5" t="inlineStr">
+    <row r="17" ht="55" customHeight="1">
+      <c r="A17" s="9" t="inlineStr">
+        <is>
+          <t>医療機関受診状況：　　　　　　服薬状況：適切/課題あり（　　　）
+体調・精神状態：安定/不安定（内容：　　　　　　）　睡眠：良好/不良
+生活環境の変化：なし / あり（　　　　　　　　）</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="20" customHeight="1">
+      <c r="A18" s="3" t="inlineStr">
+        <is>
+          <t>【本人の意向・満足度・自己評価】</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="60" customHeight="1">
+      <c r="A19" s="9" t="inlineStr">
+        <is>
+          <t>サービスへの満足度：大変満足 / 満足 / やや不満 / 不満
+「どんなことが良かった・困ったか」（本人の言葉で記録）：
+今後やってみたいこと・要望：</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="20" customHeight="1">
+      <c r="A20" s="3" t="inlineStr">
+        <is>
+          <t>【家族・支援者からの意見・要望】</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="45" customHeight="1">
+      <c r="A21" s="8" t="inlineStr"/>
+    </row>
+    <row r="22" ht="20" customHeight="1">
+      <c r="A22" s="3" t="inlineStr">
+        <is>
+          <t>【支援上の課題・改善事項】</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="55" customHeight="1">
+      <c r="A23" s="8" t="inlineStr"/>
+    </row>
+    <row r="24" ht="20" customHeight="1">
+      <c r="A24" s="3" t="inlineStr">
         <is>
           <t>【今後の支援方針・計画変更の要否】</t>
         </is>
       </c>
     </row>
-    <row r="18" ht="50" customHeight="1">
-      <c r="A18" s="6" t="inlineStr">
-        <is>
-          <t>計画変更：必要（変更内容：　　　） / 不要
-次回モニタリング予定：　　年　月　日</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="20" customHeight="1">
-      <c r="A19" s="5" t="inlineStr">
-        <is>
-          <t>【本人・家族の確認・同意】</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="30" customHeight="1">
-      <c r="A20" s="6" t="inlineStr">
-        <is>
-          <t>モニタリング結果について説明を受けました。
-署名：　　　　　　　（続柄：　　）　日付：　　年　月　日</t>
+    <row r="25" ht="50" customHeight="1">
+      <c r="A25" s="9" t="inlineStr">
+        <is>
+          <t>計画変更：必要（変更内容：　　　　　　　　） / 不要（現計画を継続）
+次期の主な支援課題・目標：</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="80" customHeight="1">
+      <c r="A26" s="8" t="inlineStr">
+        <is>
+          <t>モニタリング結果について説明を受け、確認しました。
+本人署名：　　　　　　　　（　年　月　日）　保護者・代理人：　　　　　　　続柄：　　（　年　月　日）
+サービス管理責任者署名：　　　　　　　　（実施日：　年　月　日）　管理者確認：　　　　　　（　年　月　日）</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="32">
-    <mergeCell ref="A9:H9"/>
-    <mergeCell ref="C6:D6"/>
+  <mergeCells count="29">
+    <mergeCell ref="F4:G4"/>
     <mergeCell ref="A15:H15"/>
-    <mergeCell ref="C5:D5"/>
-    <mergeCell ref="E5:F5"/>
-    <mergeCell ref="A11:H11"/>
+    <mergeCell ref="A24:H24"/>
+    <mergeCell ref="F6:G6"/>
     <mergeCell ref="A1:H1"/>
     <mergeCell ref="A6:B6"/>
-    <mergeCell ref="C4:D4"/>
-    <mergeCell ref="E4:F4"/>
-    <mergeCell ref="A7:H7"/>
+    <mergeCell ref="F7:G7"/>
+    <mergeCell ref="A7:B7"/>
+    <mergeCell ref="A25:H25"/>
     <mergeCell ref="A16:H16"/>
-    <mergeCell ref="G6:H6"/>
-    <mergeCell ref="A3:B3"/>
-    <mergeCell ref="G3:H3"/>
-    <mergeCell ref="A12:H12"/>
+    <mergeCell ref="F5:G5"/>
+    <mergeCell ref="C7:E7"/>
     <mergeCell ref="A18:H18"/>
-    <mergeCell ref="E6:F6"/>
+    <mergeCell ref="A3:H3"/>
+    <mergeCell ref="A21:H21"/>
+    <mergeCell ref="A26:H26"/>
     <mergeCell ref="A2:H2"/>
     <mergeCell ref="A5:B5"/>
-    <mergeCell ref="G5:H5"/>
     <mergeCell ref="A14:H14"/>
+    <mergeCell ref="A23:H23"/>
     <mergeCell ref="A8:H8"/>
+    <mergeCell ref="C6:E6"/>
     <mergeCell ref="A17:H17"/>
     <mergeCell ref="A4:B4"/>
-    <mergeCell ref="G4:H4"/>
+    <mergeCell ref="A22:H22"/>
+    <mergeCell ref="C5:E5"/>
     <mergeCell ref="A20:H20"/>
-    <mergeCell ref="A10:H10"/>
-    <mergeCell ref="A13:H13"/>
+    <mergeCell ref="C4:E4"/>
     <mergeCell ref="A19:H19"/>
-    <mergeCell ref="C3:D3"/>
-    <mergeCell ref="E3:F3"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
